--- a/Data/EXCEL/Transfer/bzPerformance/2024Q4/2072-bzPerformance-2024Q4.xlsx
+++ b/Data/EXCEL/Transfer/bzPerformance/2024Q4/2072-bzPerformance-2024Q4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\xls2xlsx\2024Q4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9976E357-B4E3-470B-995D-806FBAF5E0A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B93CB488-987D-4CC5-80E8-5AEDCA695766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1800" yWindow="840" windowWidth="17640" windowHeight="14310" xr2:uid="{01F243F5-767B-4456-9D9B-816FAFD3E1D8}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{FECD9DC9-B661-4E76-9E6D-2327C7DD2D33}"/>
   </bookViews>
   <sheets>
     <sheet name="2072-bzPerformance-2024Q4" sheetId="2" r:id="rId1"/>
@@ -1329,19 +1329,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{158CA093-9782-4825-9677-ED42717F2F70}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E9EF818-1365-401B-901A-4BA1D4ABF8D2}">
   <dimension ref="A1:U13"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="3" width="6.6328125" customWidth="1"/>
-    <col min="4" max="4" width="7" customWidth="1"/>
-    <col min="5" max="5" width="6.6328125" customWidth="1"/>
-    <col min="6" max="6" width="7" customWidth="1"/>
-    <col min="7" max="17" width="6.6328125" customWidth="1"/>
-    <col min="18" max="18" width="6.90625" customWidth="1"/>
-    <col min="19" max="19" width="6.6328125" customWidth="1"/>
-    <col min="20" max="20" width="7.7265625" customWidth="1"/>
-    <col min="21" max="21" width="8.81640625" customWidth="1"/>
+    <col min="1" max="3" width="11.54296875" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" customWidth="1"/>
+    <col min="5" max="5" width="11.54296875" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" customWidth="1"/>
+    <col min="7" max="17" width="11.54296875" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
+    <col min="19" max="19" width="11.54296875" customWidth="1"/>
+    <col min="20" max="20" width="13.453125" customWidth="1"/>
+    <col min="21" max="21" width="13.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
@@ -1508,16 +1508,16 @@
         <v>27</v>
       </c>
       <c r="D4" s="7">
-        <v>270</v>
+        <v>269.5</v>
       </c>
       <c r="E4" s="7">
         <v>268</v>
       </c>
       <c r="F4" s="8">
-        <v>-21</v>
+        <v>-21.5</v>
       </c>
       <c r="G4" s="8">
-        <v>-7.2</v>
+        <v>-7.4</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>27</v>
